--- a/datos_de_prueba/Ejemplo de carga masiva.xlsx
+++ b/datos_de_prueba/Ejemplo de carga masiva.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oficios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oficios'!$A$1:$Z$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oficios'!$A$1:$S$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -443,19 +443,12 @@
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="31" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="38" customWidth="1" min="16" max="16"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="33" customWidth="1" min="22" max="22"/>
-    <col width="24" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="5" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,65 +519,30 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Documento del oficio</t>
+          <t>Observación</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Respuesta en PDF</t>
+          <t>Implicado</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Observación</t>
+          <t>Tipo de identificación</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Registrado por</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Fecha de registro</t>
+          <t>Tipo de implicado</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Origen</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Anulado</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Motivo de anulación</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Implicado</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de identificación</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Identificación</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de implicado</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>LCI</t>
         </is>
@@ -613,22 +571,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -656,39 +614,32 @@
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Atendido dentro del plazo</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ORDOÑEZ VILLAGOMEZ DAVID MIGUEL</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Atendido dentro del plazo</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>ORDOÑEZ VILLAGOMEZ DAVID MIGUEL</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
           <t>Cédula</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1400349096</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -717,17 +668,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -757,34 +708,27 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>ACOSTA JEREZ DIANA CAROLINA</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Cédula</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0923847561</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -813,17 +757,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -853,34 +797,27 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>MENDOZA SALAS LUIS ALBERTO</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Cédula</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1712345678</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Ex cliente</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -909,17 +846,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -949,34 +886,27 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>QUISPE ANDRADE PEDRO JOSÉ</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Pasaporte</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>AB123456</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>No cliente</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1005,12 +935,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1032,39 +962,32 @@
           <t>Por asignar</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Pendiente de asignar</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>CEVALLOS MORA JORGE ANDRÉS</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pendiente de asignar</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>CEVALLOS MORA JORGE ANDRÉS</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
           <t>Cédula</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1309876543</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Sin identificación</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1093,22 +1016,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1136,39 +1059,32 @@
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Se remitió por correo</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>COMERCIAL LOS ANDES S.A.</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Se remitió por correo</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>COMERCIAL LOS ANDES S.A.</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
           <t>RUC</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1791234567001</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -1197,17 +1113,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1237,34 +1153,27 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>VILLACÍS ROJAS ANDREA PAOLA</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Cédula</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0102938475</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>No cliente</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -1293,17 +1202,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1333,34 +1242,27 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>ZAMBRANO LOOR KEVIN DANIEL</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Cédula</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1301122334</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1389,12 +1291,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1416,26 +1318,19 @@
           <t>Por asignar</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Llegó sin el detalle de las personas</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Llegó sin el detalle de las personas</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z10"/>
+  <autoFilter ref="A1:S10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>